--- a/artfynd/A 56179-2025 artfynd.xlsx
+++ b/artfynd/A 56179-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1668754</v>
+        <v>293985</v>
       </c>
       <c r="B2" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5754</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bastberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497116.8667595393</v>
+        <v>497133</v>
       </c>
       <c r="R2" t="n">
-        <v>6692111.003462044</v>
+        <v>6692150</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-09-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-08-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,9 +762,19 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>vid små gråalar i örtrik granskog</t>
+          <t>örtrik granskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>grov gammal talltorraka</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -798,6 +789,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1668754</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bastberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>497117</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6692111</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2009-09-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vid små gråalar i örtrik granskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
